--- a/Capstone - MATLAB Stuff/PCM_TEMP_WIND_10K_ALL_LOC.xlsx
+++ b/Capstone - MATLAB Stuff/PCM_TEMP_WIND_10K_ALL_LOC.xlsx
@@ -71,24 +71,24 @@
     <col min="13" max="13" width="5.08984375" customWidth="true"/>
     <col min="14" max="14" width="5.08984375" customWidth="true"/>
     <col min="15" max="15" width="5.08984375" customWidth="true"/>
-    <col min="16" max="16" width="5.08984375" customWidth="true"/>
+    <col min="16" max="16" width="12.08984375" customWidth="true"/>
     <col min="17" max="17" width="12.08984375" customWidth="true"/>
     <col min="18" max="18" width="12.08984375" customWidth="true"/>
-    <col min="19" max="19" width="12.08984375" customWidth="true"/>
+    <col min="19" max="19" width="14.08984375" customWidth="true"/>
     <col min="20" max="20" width="12.08984375" customWidth="true"/>
     <col min="21" max="21" width="12.08984375" customWidth="true"/>
     <col min="22" max="22" width="12.08984375" customWidth="true"/>
-    <col min="23" max="23" width="12.08984375" customWidth="true"/>
+    <col min="23" max="23" width="13.08984375" customWidth="true"/>
     <col min="24" max="24" width="12.08984375" customWidth="true"/>
     <col min="25" max="25" width="12.08984375" customWidth="true"/>
     <col min="26" max="26" width="12.08984375" customWidth="true"/>
     <col min="27" max="27" width="12.08984375" customWidth="true"/>
     <col min="28" max="28" width="12.08984375" customWidth="true"/>
-    <col min="29" max="29" width="12.08984375" customWidth="true"/>
+    <col min="29" max="29" width="13.08984375" customWidth="true"/>
     <col min="30" max="30" width="12.08984375" customWidth="true"/>
     <col min="31" max="31" width="12.08984375" customWidth="true"/>
-    <col min="32" max="32" width="12.08984375" customWidth="true"/>
-    <col min="33" max="33" width="11.08984375" customWidth="true"/>
+    <col min="32" max="32" width="11.453125" customWidth="true"/>
+    <col min="33" max="33" width="14.08984375" customWidth="true"/>
     <col min="34" max="34" width="12.08984375" customWidth="true"/>
     <col min="35" max="35" width="12.08984375" customWidth="true"/>
     <col min="36" max="36" width="5.08984375" customWidth="true"/>
@@ -165,40 +165,40 @@
         <v>-6.9000000000000004</v>
       </c>
       <c r="T1" s="0">
-        <v>-6.9000000000000004</v>
+        <v>-6.8993635949225398</v>
       </c>
       <c r="U1" s="0">
-        <v>-6.5279703354798713</v>
+        <v>-4.8323638055960041</v>
       </c>
       <c r="V1" s="0">
-        <v>-6.1560638264485261</v>
+        <v>-2.765364052947342</v>
       </c>
       <c r="W1" s="0">
-        <v>-5.7843019140559964</v>
+        <v>-0.69836432987698205</v>
       </c>
       <c r="X1" s="0">
-        <v>-5.4127018891858132</v>
+        <v>1.3686353636444175</v>
       </c>
       <c r="Y1" s="0">
-        <v>-5.0412810255683764</v>
+        <v>3.4356350635699178</v>
       </c>
       <c r="Z1" s="0">
-        <v>-4.6700355794948152</v>
+        <v>3.8068805096434795</v>
       </c>
       <c r="AA1" s="0">
-        <v>-5.0414564431122519</v>
+        <v>3.4343643298769826</v>
       </c>
       <c r="AB1" s="0">
-        <v>-5.4130564679824351</v>
+        <v>1.3673640529473423</v>
       </c>
       <c r="AC1" s="0">
-        <v>-5.7848183803749649</v>
+        <v>-0.69963619440399549</v>
       </c>
       <c r="AD1" s="0">
-        <v>-6.15672488940631</v>
+        <v>-2.7666364050774601</v>
       </c>
       <c r="AE1" s="0">
-        <v>-6.5287545539264391</v>
+        <v>-4.8336365790750548</v>
       </c>
       <c r="AF1" s="0">
         <v>-6.9000000000000004</v>
@@ -320,22 +320,22 @@
         <v>-25.199999999999999</v>
       </c>
       <c r="W2" s="0">
-        <v>-25.199999999999999</v>
+        <v>-25.197841183419431</v>
       </c>
       <c r="X2" s="0">
-        <v>-23.276950943174153</v>
+        <v>-18.197843063707502</v>
       </c>
       <c r="Y2" s="0">
-        <v>-21.355576825404235</v>
+        <v>-11.197844987326359</v>
       </c>
       <c r="Z2" s="0">
-        <v>-19.435916245255509</v>
+        <v>-9.2781844071776334</v>
       </c>
       <c r="AA2" s="0">
-        <v>-21.357290363025427</v>
+        <v>-11.202158816580569</v>
       </c>
       <c r="AB2" s="0">
-        <v>-23.280339419851274</v>
+        <v>-18.202160871781984</v>
       </c>
       <c r="AC2" s="0">
         <v>-25.199999999999999</v>
@@ -445,67 +445,67 @@
         <v>-3.6000000000000001</v>
       </c>
       <c r="P3" s="0">
-        <v>-3.6000000000000001</v>
+        <v>-3.5996368342741589</v>
       </c>
       <c r="Q3" s="0">
-        <v>-3.3877005889251422</v>
+        <v>-2.4196369143217718</v>
       </c>
       <c r="R3" s="0">
-        <v>-3.1754479720819942</v>
+        <v>-1.2396370011941409</v>
       </c>
       <c r="S3" s="0">
-        <v>-2.9632461390861611</v>
+        <v>-0.059637091649036793</v>
       </c>
       <c r="T3" s="0">
-        <v>-2.7510971842110559</v>
+        <v>1.1203628120098501</v>
       </c>
       <c r="U3" s="0">
-        <v>-2.5390045484214556</v>
+        <v>2.300362709627962</v>
       </c>
       <c r="V3" s="0">
-        <v>-2.3269717630333373</v>
+        <v>3.4803626012041993</v>
       </c>
       <c r="W3" s="0">
-        <v>-2.115002360005775</v>
+        <v>4.6603625238299857</v>
       </c>
       <c r="X3" s="0">
-        <v>-1.9030781883940109</v>
+        <v>5.8403624550364661</v>
       </c>
       <c r="Y3" s="0">
-        <v>-1.6911942320958839</v>
+        <v>7.0203623797444319</v>
       </c>
       <c r="Z3" s="0">
-        <v>-1.4793542900131638</v>
+        <v>7.2322023218271516</v>
       </c>
       <c r="AA3" s="0">
-        <v>-1.6912382463112907</v>
+        <v>7.0196374761700131</v>
       </c>
       <c r="AB3" s="0">
-        <v>-1.9031624179230548</v>
+        <v>5.8396373987958006</v>
       </c>
       <c r="AC3" s="0">
-        <v>-2.1151318209506171</v>
+        <v>4.6596372903720376</v>
       </c>
       <c r="AD3" s="0">
-        <v>-2.3271646063387355</v>
+        <v>3.4796371879901504</v>
       </c>
       <c r="AE3" s="0">
-        <v>-2.5392572421283357</v>
+        <v>2.2996370916490374</v>
       </c>
       <c r="AF3" s="0">
-        <v>-2.7514061970034409</v>
+        <v>1.1196370011941417</v>
       </c>
       <c r="AG3" s="0">
-        <v>-2.963608029999274</v>
+        <v>-0.060363085678227145</v>
       </c>
       <c r="AH3" s="0">
-        <v>-3.175860646842422</v>
+        <v>-1.2403631657258403</v>
       </c>
       <c r="AI3" s="0">
-        <v>-3.3881600579172799</v>
+        <v>-2.4203632389495069</v>
       </c>
       <c r="AJ3" s="0">
-        <v>-3.6000000000000001</v>
+        <v>-3.5999999999999988</v>
       </c>
       <c r="AK3" s="0">
         <v>-3.6000000000000001</v>
@@ -609,28 +609,28 @@
         <v>-26.199999999999999</v>
       </c>
       <c r="V4" s="0">
-        <v>-26.199999999999999</v>
+        <v>-26.198149311906633</v>
       </c>
       <c r="W4" s="0">
-        <v>-24.551428266551337</v>
+        <v>-20.198150343845917</v>
       </c>
       <c r="X4" s="0">
-        <v>-22.903775772784968</v>
+        <v>-14.198151902121701</v>
       </c>
       <c r="Y4" s="0">
-        <v>-21.257511373218943</v>
+        <v>-8.1981534678681722</v>
       </c>
       <c r="Z4" s="0">
-        <v>-19.612641722657614</v>
+        <v>-6.5532838173068422</v>
       </c>
       <c r="AA4" s="0">
-        <v>-21.258906122223639</v>
+        <v>-8.2018496561540815</v>
       </c>
       <c r="AB4" s="0">
-        <v>-22.906558615990008</v>
+        <v>-14.201850688093366</v>
       </c>
       <c r="AC4" s="0">
-        <v>-24.55513034943867</v>
+        <v>-20.201852386992133</v>
       </c>
       <c r="AD4" s="0">
         <v>-26.199999999999999</v>
